--- a/data/trans_dic/LAWTONB_2R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,47; 37,56</t>
+          <t>22,1; 38,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 32,95</t>
+          <t>17,71; 32,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,36; 27,45</t>
+          <t>14,32; 26,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,99; 40,25</t>
+          <t>28,19; 40,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,17; 38,36</t>
+          <t>23,63; 39,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,1; 45,23</t>
+          <t>30,24; 44,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,9; 43,2</t>
+          <t>27,38; 42,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,08; 51,56</t>
+          <t>42,09; 51,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,13; 36,12</t>
+          <t>24,55; 36,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,15; 37,25</t>
+          <t>26,42; 37,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,43; 33,79</t>
+          <t>23,71; 33,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,53; 45,07</t>
+          <t>37,36; 44,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,98; 40,13</t>
+          <t>25,46; 40,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,33; 37,73</t>
+          <t>22,34; 37,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,72; 31,14</t>
+          <t>18,34; 31,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,39; 31,5</t>
+          <t>21,46; 31,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,6; 45,39</t>
+          <t>30,42; 45,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,58; 53,47</t>
+          <t>38,71; 54,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,67; 44,11</t>
+          <t>30,12; 44,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,5; 46,66</t>
+          <t>37,13; 46,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,5; 41,02</t>
+          <t>30,34; 40,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,63; 44,29</t>
+          <t>33,93; 44,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,2; 36,1</t>
+          <t>26,76; 37,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,7; 39,13</t>
+          <t>31,52; 38,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 30,42</t>
+          <t>13,03; 29,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 37,83</t>
+          <t>17,9; 37,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,81; 30,54</t>
+          <t>15,78; 31,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 26,62</t>
+          <t>14,84; 26,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,58; 42,99</t>
+          <t>26,7; 42,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,36; 45,72</t>
+          <t>29,63; 46,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,05; 46,58</t>
+          <t>29,93; 47,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 40,52</t>
+          <t>4,65; 41,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,68; 34,09</t>
+          <t>22,7; 34,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,17; 39,96</t>
+          <t>26,62; 39,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,47; 37,44</t>
+          <t>25,21; 37,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 31,49</t>
+          <t>7,46; 31,89</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 27,38</t>
+          <t>15,3; 27,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 34,35</t>
+          <t>18,83; 33,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 22,39</t>
+          <t>12,08; 23,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 26,03</t>
+          <t>17,32; 26,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,29; 41,24</t>
+          <t>28,05; 40,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,69; 40,23</t>
+          <t>27,65; 40,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,79; 42,11</t>
+          <t>27,66; 41,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,16; 43,04</t>
+          <t>34,43; 43,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 34,15</t>
+          <t>24,64; 34,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,47; 36,03</t>
+          <t>26,11; 35,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,77; 32,01</t>
+          <t>22,74; 32,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,34; 34,88</t>
+          <t>28,1; 34,55</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,83; 30,2</t>
+          <t>22,92; 30,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,08; 31,0</t>
+          <t>22,81; 30,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,94; 24,15</t>
+          <t>17,87; 24,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,65; 28,14</t>
+          <t>22,59; 28,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,03</t>
+          <t>31,02; 38,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,18; 42,4</t>
+          <t>35,09; 42,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,84; 39,11</t>
+          <t>32,28; 39,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 42,22</t>
+          <t>17,41; 42,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,02; 33,51</t>
+          <t>28,22; 33,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,78; 36,16</t>
+          <t>30,76; 36,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,09; 32,14</t>
+          <t>26,86; 32,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,06; 34,9</t>
+          <t>20,6; 35,06</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24692; 43186</t>
+          <t>25413; 43876</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25323; 45985</t>
+          <t>24709; 45032</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19637; 37528</t>
+          <t>19575; 36702</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41446; 59597</t>
+          <t>41749; 60580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34645; 57357</t>
+          <t>35338; 58682</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50199; 75446</t>
+          <t>50439; 74511</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48372; 74897</t>
+          <t>47471; 73513</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74962; 91854</t>
+          <t>74982; 90985</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66465; 95543</t>
+          <t>64941; 96089</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80117; 114100</t>
+          <t>80945; 113781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72654; 104805</t>
+          <t>73530; 104536</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>122434; 147028</t>
+          <t>121879; 146680</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36437; 58545</t>
+          <t>37141; 59755</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33030; 58440</t>
+          <t>34604; 58619</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30881; 51366</t>
+          <t>30253; 51628</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32654; 50438</t>
+          <t>34368; 51193</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55900; 82914</t>
+          <t>55575; 83734</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75757; 102346</t>
+          <t>74090; 104047</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65020; 96664</t>
+          <t>66005; 98064</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81582; 101488</t>
+          <t>80767; 101266</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100223; 134786</t>
+          <t>99694; 133648</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116448; 153370</t>
+          <t>117496; 155024</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100627; 138662</t>
+          <t>102772; 142183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>119728; 147763</t>
+          <t>119042; 147180</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14417; 31754</t>
+          <t>13604; 30794</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17770; 39187</t>
+          <t>18543; 38556</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18191; 35134</t>
+          <t>18155; 36036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20172; 36062</t>
+          <t>20096; 36544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36106; 58403</t>
+          <t>36277; 57224</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41399; 64473</t>
+          <t>41779; 65511</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42853; 66418</t>
+          <t>42675; 68105</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16714; 145799</t>
+          <t>16723; 149080</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52069; 81887</t>
+          <t>54535; 83205</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66466; 97748</t>
+          <t>65120; 97154</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65612; 96448</t>
+          <t>64941; 96523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32719; 155972</t>
+          <t>36968; 157919</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20579; 37576</t>
+          <t>20992; 38371</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31472; 55519</t>
+          <t>30426; 54845</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20838; 39092</t>
+          <t>21099; 40298</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34521; 52254</t>
+          <t>34763; 52202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59062; 86094</t>
+          <t>58555; 85338</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67494; 98063</t>
+          <t>67393; 97906</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67479; 102237</t>
+          <t>67149; 100876</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>93526; 117831</t>
+          <t>94249; 118477</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84479; 118162</t>
+          <t>85250; 118466</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>107295; 146036</t>
+          <t>105849; 143336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95046; 133612</t>
+          <t>94920; 133584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>134466; 165501</t>
+          <t>133344; 163935</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>114697; 151761</t>
+          <t>115143; 152959</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>129139; 173471</t>
+          <t>127667; 172407</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106103; 142797</t>
+          <t>105641; 143942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145980; 181314</t>
+          <t>145589; 180902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>207894; 257407</t>
+          <t>209951; 260274</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>261377; 315014</t>
+          <t>260717; 316377</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>247689; 304264</t>
+          <t>251097; 306449</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>178478; 434506</t>
+          <t>179236; 433745</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>330432; 395194</t>
+          <t>332744; 395723</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>400951; 471055</t>
+          <t>400732; 470735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>370897; 440086</t>
+          <t>367801; 438824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>352520; 584126</t>
+          <t>344724; 586783</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,1; 38,16</t>
+          <t>21,68; 38,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 32,27</t>
+          <t>17,46; 32,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 26,84</t>
+          <t>13,82; 26,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 40,91</t>
+          <t>27,33; 39,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,63; 39,24</t>
+          <t>23,45; 38,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,24; 44,67</t>
+          <t>30,24; 44,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,38; 42,4</t>
+          <t>27,06; 42,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,09; 51,08</t>
+          <t>42,02; 51,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,55; 36,33</t>
+          <t>24,81; 36,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,42; 37,14</t>
+          <t>26,19; 37,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 33,71</t>
+          <t>23,23; 34,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,36; 44,96</t>
+          <t>36,57; 44,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,46; 40,96</t>
+          <t>25,8; 41,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,34; 37,85</t>
+          <t>22,23; 37,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,34; 31,3</t>
+          <t>19,32; 31,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,46; 31,97</t>
+          <t>20,08; 30,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,42; 45,84</t>
+          <t>30,35; 44,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,71; 54,36</t>
+          <t>39,85; 53,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,12; 44,74</t>
+          <t>29,75; 43,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,13; 46,55</t>
+          <t>37,06; 46,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,34; 40,68</t>
+          <t>30,4; 41,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,93; 44,77</t>
+          <t>33,76; 44,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,76; 37,02</t>
+          <t>26,53; 36,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,52; 38,97</t>
+          <t>31,38; 38,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,03; 29,5</t>
+          <t>13,31; 29,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,9; 37,22</t>
+          <t>17,98; 37,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,78; 31,33</t>
+          <t>15,87; 31,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 26,98</t>
+          <t>15,19; 27,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,7; 42,12</t>
+          <t>26,64; 42,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,63; 46,46</t>
+          <t>28,58; 46,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,93; 47,76</t>
+          <t>29,46; 46,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 41,43</t>
+          <t>32,99; 44,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,7; 34,64</t>
+          <t>22,4; 34,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,62; 39,72</t>
+          <t>26,65; 38,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,21; 37,47</t>
+          <t>25,39; 37,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 31,89</t>
+          <t>25,78; 34,49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,3; 27,96</t>
+          <t>14,28; 27,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 33,94</t>
+          <t>19,56; 34,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,08; 23,08</t>
+          <t>12,19; 23,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,32; 26,0</t>
+          <t>16,62; 25,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 40,88</t>
+          <t>27,74; 40,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,65; 40,17</t>
+          <t>27,66; 40,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,66; 41,55</t>
+          <t>27,76; 41,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,43; 43,28</t>
+          <t>35,08; 43,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,64; 34,24</t>
+          <t>24,27; 33,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,11; 35,36</t>
+          <t>26,15; 35,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,74; 32,0</t>
+          <t>22,81; 32,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 34,55</t>
+          <t>28,17; 34,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,92; 30,44</t>
+          <t>22,74; 30,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,81; 30,81</t>
+          <t>22,85; 30,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,34</t>
+          <t>17,9; 24,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,59; 28,07</t>
+          <t>22,38; 27,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,45</t>
+          <t>30,92; 38,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,09; 42,58</t>
+          <t>34,82; 42,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,28; 39,39</t>
+          <t>31,89; 39,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,41; 42,14</t>
+          <t>38,85; 43,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,22; 33,56</t>
+          <t>28,38; 33,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,76; 36,14</t>
+          <t>30,78; 36,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,86; 32,05</t>
+          <t>26,61; 31,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,6; 35,06</t>
+          <t>32,18; 35,88</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50528</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83070</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>133599</t>
+          <t>142270</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25413; 43876</t>
+          <t>24925; 43757</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24709; 45032</t>
+          <t>24359; 45662</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19575; 36702</t>
+          <t>18901; 36822</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41749; 60580</t>
+          <t>44628; 63885</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35338; 58682</t>
+          <t>35063; 57348</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50439; 74511</t>
+          <t>50430; 74756</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47471; 73513</t>
+          <t>46922; 73449</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74982; 90985</t>
+          <t>79747; 97506</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64941; 96089</t>
+          <t>65638; 96202</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80945; 113781</t>
+          <t>80241; 113651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73530; 104536</t>
+          <t>72033; 105442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>121879; 146680</t>
+          <t>129146; 156118</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90897</t>
+          <t>100236</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>132642</t>
+          <t>145374</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37141; 59755</t>
+          <t>37644; 60003</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34604; 58619</t>
+          <t>34435; 57587</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30253; 51628</t>
+          <t>31861; 51669</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34368; 51193</t>
+          <t>35784; 55189</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55575; 83734</t>
+          <t>55446; 81982</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74090; 104047</t>
+          <t>76289; 102934</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66005; 98064</t>
+          <t>65197; 95949</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80767; 101266</t>
+          <t>89206; 111916</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99694; 133648</t>
+          <t>99878; 135662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117496; 155024</t>
+          <t>116908; 153795</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102772; 142183</t>
+          <t>101921; 141297</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>119042; 147180</t>
+          <t>131477; 161035</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61010</t>
+          <t>67756</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88668</t>
+          <t>99994</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13604; 30794</t>
+          <t>13889; 30429</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18543; 38556</t>
+          <t>18627; 39056</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18155; 36036</t>
+          <t>18255; 35889</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20096; 36544</t>
+          <t>24019; 43027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36277; 57224</t>
+          <t>36194; 57922</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41779; 65511</t>
+          <t>40296; 65126</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42675; 68105</t>
+          <t>42010; 66971</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16723; 149080</t>
+          <t>57546; 77911</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54535; 83205</t>
+          <t>53800; 82350</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65120; 97154</t>
+          <t>65199; 95266</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64941; 96523</t>
+          <t>65403; 97168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36968; 157919</t>
+          <t>85753; 114700</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43074</t>
+          <t>44178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>105910</t>
+          <t>114402</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>148984</t>
+          <t>158581</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20992; 38371</t>
+          <t>19598; 38406</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30426; 54845</t>
+          <t>31607; 55171</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21099; 40298</t>
+          <t>21282; 40780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34763; 52202</t>
+          <t>34988; 53404</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58555; 85338</t>
+          <t>57920; 85470</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67393; 97906</t>
+          <t>67410; 97516</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67149; 100876</t>
+          <t>67403; 99768</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94249; 118477</t>
+          <t>102858; 127546</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85250; 118466</t>
+          <t>83986; 116717</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>105849; 143336</t>
+          <t>106022; 143724</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94920; 133584</t>
+          <t>95203; 133687</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>133344; 163935</t>
+          <t>141899; 174508</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>175457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>340887</t>
+          <t>370762</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>503892</t>
+          <t>546218</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>115143; 152959</t>
+          <t>114256; 153418</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>127667; 172407</t>
+          <t>127896; 172620</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105641; 143942</t>
+          <t>105867; 143017</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145589; 180902</t>
+          <t>158954; 197033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>209951; 260274</t>
+          <t>209277; 259970</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>260717; 316377</t>
+          <t>258686; 313752</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>251097; 306449</t>
+          <t>248112; 305455</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>179236; 433745</t>
+          <t>348962; 390260</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>332744; 395723</t>
+          <t>334693; 394645</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>400732; 470735</t>
+          <t>400904; 469767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>367801; 438824</t>
+          <t>364334; 433164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>344724; 586783</t>
+          <t>517575; 577032</t>
         </is>
       </c>
     </row>
